--- a/screening_data/sample_key.xlsx
+++ b/screening_data/sample_key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/screening_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F552DFF-E136-FC47-A35B-E39E12E88EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083E57D8-7683-314C-A8DE-B3DA32F0FEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{7BB4DE15-1F1C-D742-8C62-FDC872071E1C}"/>
   </bookViews>
@@ -742,6 +742,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF212121"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
     </font>
@@ -753,27 +758,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF212121"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF191919"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF212121"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -802,15 +802,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,10 +1149,11 @@
   <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="1" max="2" width="57" style="3" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1178,13 +1180,13 @@
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1195,13 +1197,13 @@
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1212,13 +1214,13 @@
       <c r="B4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1229,13 +1231,13 @@
       <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1246,13 +1248,13 @@
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1263,13 +1265,13 @@
       <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1280,13 +1282,13 @@
       <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1297,13 +1299,13 @@
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1314,13 +1316,13 @@
       <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1331,13 +1333,13 @@
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1348,13 +1350,13 @@
       <c r="B12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1365,13 +1367,13 @@
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1382,13 +1384,13 @@
       <c r="B14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1399,13 +1401,13 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1416,13 +1418,13 @@
       <c r="B16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1433,13 +1435,13 @@
       <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1450,13 +1452,13 @@
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1467,13 +1469,13 @@
       <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1484,13 +1486,13 @@
       <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1501,13 +1503,13 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1518,13 +1520,13 @@
       <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1535,13 +1537,13 @@
       <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1552,13 +1554,13 @@
       <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1569,13 +1571,13 @@
       <c r="B25" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1586,13 +1588,13 @@
       <c r="B26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1603,13 +1605,13 @@
       <c r="B27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1620,13 +1622,13 @@
       <c r="B28" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1637,13 +1639,13 @@
       <c r="B29" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1654,13 +1656,13 @@
       <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1671,1684 +1673,1684 @@
       <c r="B31" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>107</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C34" t="s">
-        <v>107</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>107</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C54" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C55" t="s">
-        <v>107</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C56" t="s">
-        <v>107</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C57" t="s">
-        <v>107</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C59" t="s">
-        <v>107</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C59" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C60" t="s">
-        <v>107</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C60" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C61" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C61" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
+      <c r="E61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="C62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="C63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C64" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="C64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C65" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C65" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C66" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C67" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C67" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C68" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C69" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C71" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="C71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C72" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C73" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C73" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C74" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C74" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C75" t="s">
-        <v>107</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C75" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C76" t="s">
-        <v>107</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="C76" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C77" t="s">
-        <v>107</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="C77" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C78" t="s">
-        <v>107</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C78" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C79" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C80" t="s">
-        <v>107</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C80" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C81" t="s">
-        <v>107</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="C81" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C82" t="s">
-        <v>107</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="C82" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="C83" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C84" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C85" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C86" t="s">
-        <v>107</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C86" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+      <c r="E86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C87" t="s">
-        <v>2</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
+      <c r="E87" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C88" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+      <c r="E88" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C89" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+      <c r="E89" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="E90" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C91" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
+      <c r="E91" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C92" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C92" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
+      <c r="E92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C93" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
+      <c r="E93" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C94" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C94" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
+      <c r="E94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
+      <c r="E95" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C96" t="s">
-        <v>2</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
+      <c r="E96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A97" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C97" t="s">
-        <v>2</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
+      <c r="E97" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C98" t="s">
-        <v>2</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="C98" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
+      <c r="E98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C99" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="C99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
+      <c r="E99" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C100" t="s">
-        <v>2</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="C100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+      <c r="E100" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C101" t="s">
-        <v>2</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+      <c r="E101" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+      <c r="E102" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+      <c r="E103" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+      <c r="E104" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C105" t="s">
-        <v>2</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
+      <c r="E105" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C106" t="s">
-        <v>2</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
+      <c r="E106" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C107" t="s">
-        <v>2</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
+      <c r="E107" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C108" t="s">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+      <c r="E108" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E109">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
+      <c r="E109" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C110" t="s">
-        <v>2</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="E110" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C111" t="s">
-        <v>2</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C111" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E111">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+      <c r="E111" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C112" t="s">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="C112" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E112">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
+      <c r="E112" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C113" t="s">
-        <v>2</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="C113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
+      <c r="E113" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C114" t="s">
-        <v>107</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="C114" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+      <c r="E114" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C115" t="s">
-        <v>107</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C115" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
+      <c r="E115" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C116" t="s">
-        <v>107</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C116" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E116">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
+      <c r="E116" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C117" t="s">
-        <v>107</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="C117" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
+      <c r="E117" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C118" t="s">
-        <v>107</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="C118" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E118">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
+      <c r="E118" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C119" t="s">
-        <v>107</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="C119" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E119">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
+      <c r="E119" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C120" t="s">
-        <v>107</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="C120" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E120">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
+      <c r="E120" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C121" t="s">
-        <v>107</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="C121" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
+      <c r="E121" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C122" t="s">
-        <v>107</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="C122" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
+      <c r="E122" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C123" t="s">
-        <v>107</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="C123" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
+      <c r="E123" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C124" t="s">
-        <v>107</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="C124" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
+      <c r="E124" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C125" t="s">
-        <v>107</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="C125" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
+      <c r="E125" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C126" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="C126" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
+      <c r="E126" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C127" t="s">
-        <v>107</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="C127" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
+      <c r="E127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C128" t="s">
-        <v>107</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C128" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="20" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
+      <c r="E128" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="3">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/screening_data/sample_key.xlsx
+++ b/screening_data/sample_key.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samgould/Documents/GitHub/CDK-BE-mutagenesis/screening_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BAAB97-A8F8-FF44-98E6-7F4216E4714C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287EB957-F0F7-E34D-8BBC-9075F659527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{7BB4DE15-1F1C-D742-8C62-FDC872071E1C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="307">
   <si>
     <t>Sample</t>
   </si>
@@ -699,13 +699,271 @@
   </si>
   <si>
     <t>CDK12_13</t>
+  </si>
+  <si>
+    <t>CDK2_4_6</t>
+  </si>
+  <si>
+    <t>D25-213001</t>
+  </si>
+  <si>
+    <t>CBE_ABEMA_REP1</t>
+  </si>
+  <si>
+    <t>D25-213002</t>
+  </si>
+  <si>
+    <t>CBE_ABEMA_REP2</t>
+  </si>
+  <si>
+    <t>D25-213003</t>
+  </si>
+  <si>
+    <t>CBE_ABEMA_REP3</t>
+  </si>
+  <si>
+    <t>D25-213004</t>
+  </si>
+  <si>
+    <t>CBE_ATIRMO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213005</t>
+  </si>
+  <si>
+    <t>CBE_ATIRMO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213006</t>
+  </si>
+  <si>
+    <t>CBE_ATIRMO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213007</t>
+  </si>
+  <si>
+    <t>CBE_PALBO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213008</t>
+  </si>
+  <si>
+    <t>CBE_PALBO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213009</t>
+  </si>
+  <si>
+    <t>CBE_PALBO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213010</t>
+  </si>
+  <si>
+    <t>CBE_TAGTO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213011</t>
+  </si>
+  <si>
+    <t>CBE_TAGTO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213012</t>
+  </si>
+  <si>
+    <t>CBE_TAGTO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213013</t>
+  </si>
+  <si>
+    <t>CBE_INX_REP1</t>
+  </si>
+  <si>
+    <t>D25-213014</t>
+  </si>
+  <si>
+    <t>CBE_INX_REP2</t>
+  </si>
+  <si>
+    <t>D25-213015</t>
+  </si>
+  <si>
+    <t>CBE_INX_REP3</t>
+  </si>
+  <si>
+    <t>D25-213016</t>
+  </si>
+  <si>
+    <t>D25-213017</t>
+  </si>
+  <si>
+    <t>D25-213018</t>
+  </si>
+  <si>
+    <t>D25-213019</t>
+  </si>
+  <si>
+    <t>D25-213020</t>
+  </si>
+  <si>
+    <t>D25-213021</t>
+  </si>
+  <si>
+    <t>D25-213022</t>
+  </si>
+  <si>
+    <t>ABE_RIBO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213023</t>
+  </si>
+  <si>
+    <t>ABE_RIBO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213024</t>
+  </si>
+  <si>
+    <t>ABE_RIBO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213025</t>
+  </si>
+  <si>
+    <t>ABE_ABEMA_REP1</t>
+  </si>
+  <si>
+    <t>D25-213026</t>
+  </si>
+  <si>
+    <t>ABE_ABEMA_REP2</t>
+  </si>
+  <si>
+    <t>D25-213027</t>
+  </si>
+  <si>
+    <t>ABE_ABEMA_REP3</t>
+  </si>
+  <si>
+    <t>D25-213028</t>
+  </si>
+  <si>
+    <t>ABE_ATIRMO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213029</t>
+  </si>
+  <si>
+    <t>ABE_ATIRMO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213030</t>
+  </si>
+  <si>
+    <t>ABE_ATIRMO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213031</t>
+  </si>
+  <si>
+    <t>ABE_PALBO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213032</t>
+  </si>
+  <si>
+    <t>ABE_PALBO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213033</t>
+  </si>
+  <si>
+    <t>ABE_PALBO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213034</t>
+  </si>
+  <si>
+    <t>ABE_TAGTO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213035</t>
+  </si>
+  <si>
+    <t>ABE_TAGTO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213036</t>
+  </si>
+  <si>
+    <t>ABE_TAGTO_REP3</t>
+  </si>
+  <si>
+    <t>D25-213037</t>
+  </si>
+  <si>
+    <t>ABE_INX_REP1</t>
+  </si>
+  <si>
+    <t>D25-213038</t>
+  </si>
+  <si>
+    <t>ABE_INX_REP2</t>
+  </si>
+  <si>
+    <t>D25-213039</t>
+  </si>
+  <si>
+    <t>ABE_INX_REP3</t>
+  </si>
+  <si>
+    <t>D25-213040</t>
+  </si>
+  <si>
+    <t>D25-213041</t>
+  </si>
+  <si>
+    <t>D25-213042</t>
+  </si>
+  <si>
+    <t>D25-213043</t>
+  </si>
+  <si>
+    <t>D25-213044</t>
+  </si>
+  <si>
+    <t>D25-213045</t>
+  </si>
+  <si>
+    <t>D25-213046</t>
+  </si>
+  <si>
+    <t>D25-213047</t>
+  </si>
+  <si>
+    <t>CBE_RIBO_REP1</t>
+  </si>
+  <si>
+    <t>D25-213048</t>
+  </si>
+  <si>
+    <t>CBE_RIBO_REP2</t>
+  </si>
+  <si>
+    <t>D25-213049</t>
+  </si>
+  <si>
+    <t>CBE_RIBO_REP3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -748,6 +1006,14 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -775,15 +1041,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1118,13 +1393,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB374FE4-B3C2-9A49-B040-5119B64D679F}">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:J333"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="1" max="2" width="57" style="8" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -1151,13 +1427,13 @@
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1168,13 +1444,13 @@
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1185,13 +1461,13 @@
       <c r="B4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1202,13 +1478,13 @@
       <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1219,13 +1495,13 @@
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1236,13 +1512,13 @@
       <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1253,13 +1529,13 @@
       <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1270,13 +1546,13 @@
       <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1287,13 +1563,13 @@
       <c r="B10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1304,13 +1580,13 @@
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1321,13 +1597,13 @@
       <c r="B12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1338,13 +1614,13 @@
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1355,13 +1631,13 @@
       <c r="B14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1372,13 +1648,13 @@
       <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1389,13 +1665,13 @@
       <c r="B16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1406,13 +1682,13 @@
       <c r="B17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1423,13 +1699,13 @@
       <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1440,13 +1716,13 @@
       <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1457,13 +1733,13 @@
       <c r="B20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1474,13 +1750,13 @@
       <c r="B21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1491,13 +1767,13 @@
       <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1508,13 +1784,13 @@
       <c r="B23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1525,13 +1801,13 @@
       <c r="B24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1542,13 +1818,13 @@
       <c r="B25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1559,13 +1835,13 @@
       <c r="B26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1576,13 +1852,13 @@
       <c r="B27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1593,13 +1869,13 @@
       <c r="B28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1610,13 +1886,13 @@
       <c r="B29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C29" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1627,13 +1903,13 @@
       <c r="B30" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1644,13 +1920,13 @@
       <c r="B31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1658,16 +1934,16 @@
       <c r="A32" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1675,16 +1951,16 @@
       <c r="A33" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1692,16 +1968,16 @@
       <c r="A34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1709,16 +1985,16 @@
       <c r="A35" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1726,16 +2002,16 @@
       <c r="A36" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1743,16 +2019,16 @@
       <c r="A37" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1760,16 +2036,16 @@
       <c r="A38" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1777,16 +2053,16 @@
       <c r="A39" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1794,16 +2070,16 @@
       <c r="A40" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1811,16 +2087,16 @@
       <c r="A41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1828,16 +2104,16 @@
       <c r="A42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1845,16 +2121,16 @@
       <c r="A43" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1862,16 +2138,16 @@
       <c r="A44" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1879,16 +2155,16 @@
       <c r="A45" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1896,16 +2172,16 @@
       <c r="A46" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1913,16 +2189,16 @@
       <c r="A47" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1930,16 +2206,16 @@
       <c r="A48" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1947,16 +2223,16 @@
       <c r="A49" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1964,16 +2240,16 @@
       <c r="A50" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>98</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1981,16 +2257,16 @@
       <c r="A51" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="8">
         <v>1</v>
       </c>
     </row>
@@ -1998,16 +2274,16 @@
       <c r="A52" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2015,16 +2291,16 @@
       <c r="A53" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C53" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2032,16 +2308,16 @@
       <c r="A54" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2049,16 +2325,16 @@
       <c r="A55" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C55" t="s">
-        <v>98</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2066,16 +2342,16 @@
       <c r="A56" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C56" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2083,16 +2359,16 @@
       <c r="A57" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C57" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2100,16 +2376,16 @@
       <c r="A58" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C58" t="s">
-        <v>98</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2117,16 +2393,16 @@
       <c r="A59" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C59" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C59" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2134,16 +2410,16 @@
       <c r="A60" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C60" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C60" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="8">
         <v>1</v>
       </c>
     </row>
@@ -2151,1174 +2427,3555 @@
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C61" t="s">
-        <v>98</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C61" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E61" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D62" s="5" t="s">
+      <c r="C62" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="C63" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C64" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="C64" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C65" t="s">
-        <v>2</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C65" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C66" t="s">
-        <v>2</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C66" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C67" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C67" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C68" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C68" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C69" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C69" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C70" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C71" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="C71" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C72" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C72" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C73" t="s">
-        <v>2</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C73" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C74" t="s">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C74" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C75" t="s">
-        <v>98</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C75" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C76" t="s">
-        <v>98</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="C76" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D76" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C77" t="s">
-        <v>98</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="C77" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D77" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C78" t="s">
-        <v>98</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C78" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C79" t="s">
-        <v>98</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C79" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D79" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C80" t="s">
-        <v>98</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C80" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C81" t="s">
-        <v>98</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="C81" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C82" t="s">
-        <v>98</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="C82" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C83" t="s">
-        <v>98</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="C83" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D83" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C84" t="s">
-        <v>98</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C84" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D84" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="C85" t="s">
-        <v>98</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C85" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C86" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D86" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C87" t="s">
-        <v>2</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C87" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C88" t="s">
-        <v>2</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C88" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C89" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C89" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C90" t="s">
-        <v>2</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C90" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C91" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C91" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C92" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C92" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C93" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="C94" t="s">
-        <v>2</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C94" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C95" t="s">
-        <v>2</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C95" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C96" t="s">
-        <v>2</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C96" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C97" t="s">
-        <v>2</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C97" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C98" t="s">
-        <v>2</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="C98" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C99" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="C99" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C100" t="s">
-        <v>2</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="C100" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C101" t="s">
-        <v>2</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C101" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C102" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C103" t="s">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C103" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C104" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C105" t="s">
-        <v>2</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C105" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C106" t="s">
-        <v>2</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C106" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C107" t="s">
-        <v>2</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C107" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C108" t="s">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C108" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C109" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C110" t="s">
-        <v>2</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C111" t="s">
-        <v>2</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C111" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C112" t="s">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="C112" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E112">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="7" t="s">
+      <c r="E112" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A113" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C113" t="s">
-        <v>2</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="C113" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="7" t="s">
+      <c r="E113" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C114" t="s">
-        <v>98</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="C114" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D114" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="7" t="s">
+      <c r="E114" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A115" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C115" t="s">
-        <v>98</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C115" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D115" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="7" t="s">
+      <c r="E115" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C116" t="s">
-        <v>98</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C116" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D116" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E116">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="7" t="s">
+      <c r="E116" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A117" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C117" t="s">
-        <v>98</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="C117" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D117" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="7" t="s">
+      <c r="E117" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A118" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C118" t="s">
-        <v>98</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="C118" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D118" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E118">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="7" t="s">
+      <c r="E118" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A119" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C119" t="s">
-        <v>98</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="C119" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D119" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E119">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="7" t="s">
+      <c r="E119" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A120" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C120" t="s">
-        <v>98</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="C120" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D120" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E120">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="7" t="s">
+      <c r="E120" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A121" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C121" t="s">
-        <v>98</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="C121" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D121" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="7" t="s">
+      <c r="E121" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A122" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C122" t="s">
-        <v>98</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="C122" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D122" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A123" s="7" t="s">
+      <c r="E122" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A123" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C123" t="s">
-        <v>98</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="C123" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D123" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="7" t="s">
+      <c r="E123" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A124" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C124" t="s">
-        <v>98</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="C124" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D124" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E124" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C125" t="s">
-        <v>98</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="C125" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D125" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E125" s="10">
+        <v>2</v>
+      </c>
+      <c r="F125" s="10"/>
+      <c r="G125" s="10"/>
+      <c r="H125" s="10"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C126" t="s">
-        <v>98</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="C126" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D126" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E126" s="10">
+        <v>2</v>
+      </c>
+      <c r="F126" s="10"/>
+      <c r="G126" s="10"/>
+      <c r="H126" s="10"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C127" t="s">
-        <v>98</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="C127" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D127" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E127" s="10">
+        <v>2</v>
+      </c>
+      <c r="F127" s="10"/>
+      <c r="G127" s="10"/>
+      <c r="H127" s="10"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C128" t="s">
-        <v>98</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C128" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D128" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E128" s="10">
+        <v>2</v>
+      </c>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
+      <c r="H128" s="10"/>
+      <c r="I128" s="10"/>
+      <c r="J128" s="10"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E129">
-        <v>2</v>
-      </c>
+      <c r="E129" s="10">
+        <v>2</v>
+      </c>
+      <c r="F129" s="10"/>
+      <c r="G129" s="10"/>
+      <c r="H129" s="10"/>
+      <c r="I129" s="10"/>
+      <c r="J129" s="10"/>
+    </row>
+    <row r="130" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A130" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E130" s="10">
+        <v>3</v>
+      </c>
+      <c r="F130" s="10"/>
+      <c r="G130" s="10"/>
+      <c r="H130" s="10"/>
+      <c r="I130" s="10"/>
+      <c r="J130" s="10"/>
+    </row>
+    <row r="131" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A131" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E131" s="10">
+        <v>3</v>
+      </c>
+      <c r="F131" s="10"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
+      <c r="I131" s="12"/>
+      <c r="J131" s="10"/>
+    </row>
+    <row r="132" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A132" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E132" s="10">
+        <v>3</v>
+      </c>
+      <c r="F132" s="10"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="10"/>
+    </row>
+    <row r="133" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A133" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E133" s="10">
+        <v>3</v>
+      </c>
+      <c r="F133" s="10"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="10"/>
+    </row>
+    <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E134" s="10">
+        <v>3</v>
+      </c>
+      <c r="F134" s="10"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="11"/>
+      <c r="I134" s="11"/>
+      <c r="J134" s="10"/>
+    </row>
+    <row r="135" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E135" s="10">
+        <v>3</v>
+      </c>
+      <c r="F135" s="10"/>
+      <c r="G135" s="12"/>
+      <c r="H135" s="11"/>
+      <c r="I135" s="11"/>
+      <c r="J135" s="10"/>
+    </row>
+    <row r="136" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A136" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E136" s="10">
+        <v>3</v>
+      </c>
+      <c r="F136" s="10"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="11"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="10"/>
+    </row>
+    <row r="137" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A137" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E137" s="10">
+        <v>3</v>
+      </c>
+      <c r="F137" s="10"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="11"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="10"/>
+    </row>
+    <row r="138" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A138" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E138" s="10">
+        <v>3</v>
+      </c>
+      <c r="F138" s="10"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="10"/>
+    </row>
+    <row r="139" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A139" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D139" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E139" s="10">
+        <v>3</v>
+      </c>
+      <c r="F139" s="10"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="10"/>
+    </row>
+    <row r="140" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A140" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E140" s="10">
+        <v>3</v>
+      </c>
+      <c r="F140" s="10"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="10"/>
+    </row>
+    <row r="141" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A141" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E141" s="10">
+        <v>3</v>
+      </c>
+      <c r="F141" s="10"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="10"/>
+    </row>
+    <row r="142" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A142" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E142" s="10">
+        <v>3</v>
+      </c>
+      <c r="F142" s="10"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="10"/>
+    </row>
+    <row r="143" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A143" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D143" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E143" s="10">
+        <v>3</v>
+      </c>
+      <c r="F143" s="10"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="10"/>
+    </row>
+    <row r="144" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A144" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E144" s="10">
+        <v>3</v>
+      </c>
+      <c r="F144" s="10"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="11"/>
+      <c r="I144" s="11"/>
+      <c r="J144" s="10"/>
+    </row>
+    <row r="145" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A145" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E145" s="10">
+        <v>3</v>
+      </c>
+      <c r="F145" s="10"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="11"/>
+      <c r="J145" s="10"/>
+    </row>
+    <row r="146" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A146" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E146" s="10">
+        <v>3</v>
+      </c>
+      <c r="F146" s="10"/>
+      <c r="G146" s="12"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="10"/>
+    </row>
+    <row r="147" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A147" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E147" s="10">
+        <v>3</v>
+      </c>
+      <c r="F147" s="10"/>
+      <c r="G147" s="12"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="10"/>
+    </row>
+    <row r="148" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A148" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E148" s="10">
+        <v>3</v>
+      </c>
+      <c r="F148" s="10"/>
+      <c r="G148" s="12"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="10"/>
+    </row>
+    <row r="149" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A149" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E149" s="10">
+        <v>3</v>
+      </c>
+      <c r="F149" s="10"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="11"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="10"/>
+    </row>
+    <row r="150" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A150" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E150" s="10">
+        <v>3</v>
+      </c>
+      <c r="F150" s="10"/>
+      <c r="G150" s="12"/>
+      <c r="H150" s="11"/>
+      <c r="I150" s="11"/>
+      <c r="J150" s="10"/>
+    </row>
+    <row r="151" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A151" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E151" s="10">
+        <v>3</v>
+      </c>
+      <c r="F151" s="10"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="11"/>
+      <c r="I151" s="11"/>
+      <c r="J151" s="10"/>
+    </row>
+    <row r="152" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A152" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E152" s="10">
+        <v>3</v>
+      </c>
+      <c r="F152" s="10"/>
+      <c r="G152" s="12"/>
+      <c r="H152" s="11"/>
+      <c r="I152" s="11"/>
+      <c r="J152" s="10"/>
+    </row>
+    <row r="153" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A153" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E153" s="10">
+        <v>3</v>
+      </c>
+      <c r="F153" s="10"/>
+      <c r="G153" s="12"/>
+      <c r="H153" s="11"/>
+      <c r="I153" s="11"/>
+      <c r="J153" s="10"/>
+    </row>
+    <row r="154" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A154" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D154" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E154" s="10">
+        <v>3</v>
+      </c>
+      <c r="F154" s="10"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="11"/>
+      <c r="I154" s="11"/>
+      <c r="J154" s="10"/>
+    </row>
+    <row r="155" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A155" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E155" s="10">
+        <v>3</v>
+      </c>
+      <c r="F155" s="10"/>
+      <c r="G155" s="12"/>
+      <c r="H155" s="11"/>
+      <c r="I155" s="11"/>
+      <c r="J155" s="10"/>
+    </row>
+    <row r="156" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A156" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E156" s="10">
+        <v>3</v>
+      </c>
+      <c r="F156" s="10"/>
+      <c r="G156" s="12"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="10"/>
+    </row>
+    <row r="157" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A157" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D157" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E157" s="10">
+        <v>3</v>
+      </c>
+      <c r="F157" s="10"/>
+      <c r="G157" s="12"/>
+      <c r="H157" s="11"/>
+      <c r="I157" s="11"/>
+      <c r="J157" s="10"/>
+    </row>
+    <row r="158" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A158" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E158" s="10">
+        <v>3</v>
+      </c>
+      <c r="F158" s="10"/>
+      <c r="G158" s="12"/>
+      <c r="H158" s="11"/>
+      <c r="I158" s="11"/>
+      <c r="J158" s="10"/>
+    </row>
+    <row r="159" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A159" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E159" s="10">
+        <v>3</v>
+      </c>
+      <c r="F159" s="10"/>
+      <c r="G159" s="12"/>
+      <c r="H159" s="11"/>
+      <c r="I159" s="11"/>
+      <c r="J159" s="10"/>
+    </row>
+    <row r="160" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A160" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E160" s="10">
+        <v>3</v>
+      </c>
+      <c r="F160" s="10"/>
+      <c r="G160" s="12"/>
+      <c r="H160" s="11"/>
+      <c r="I160" s="11"/>
+      <c r="J160" s="10"/>
+    </row>
+    <row r="161" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A161" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E161" s="10">
+        <v>3</v>
+      </c>
+      <c r="F161" s="10"/>
+      <c r="G161" s="12"/>
+      <c r="H161" s="11"/>
+      <c r="I161" s="11"/>
+      <c r="J161" s="10"/>
+    </row>
+    <row r="162" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A162" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E162" s="10">
+        <v>3</v>
+      </c>
+      <c r="F162" s="10"/>
+      <c r="G162" s="12"/>
+      <c r="H162" s="11"/>
+      <c r="I162" s="11"/>
+      <c r="J162" s="10"/>
+    </row>
+    <row r="163" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A163" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E163" s="10">
+        <v>3</v>
+      </c>
+      <c r="F163" s="10"/>
+      <c r="G163" s="12"/>
+      <c r="H163" s="11"/>
+      <c r="I163" s="11"/>
+      <c r="J163" s="10"/>
+    </row>
+    <row r="164" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A164" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E164" s="10">
+        <v>3</v>
+      </c>
+      <c r="F164" s="10"/>
+      <c r="G164" s="12"/>
+      <c r="H164" s="11"/>
+      <c r="I164" s="11"/>
+      <c r="J164" s="10"/>
+    </row>
+    <row r="165" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A165" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E165" s="10">
+        <v>3</v>
+      </c>
+      <c r="F165" s="10"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="11"/>
+      <c r="I165" s="11"/>
+      <c r="J165" s="10"/>
+    </row>
+    <row r="166" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A166" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E166" s="10">
+        <v>3</v>
+      </c>
+      <c r="F166" s="10"/>
+      <c r="G166" s="12"/>
+      <c r="H166" s="11"/>
+      <c r="I166" s="11"/>
+      <c r="J166" s="10"/>
+    </row>
+    <row r="167" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A167" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E167" s="10">
+        <v>3</v>
+      </c>
+      <c r="F167" s="10"/>
+      <c r="G167" s="12"/>
+      <c r="H167" s="11"/>
+      <c r="I167" s="11"/>
+      <c r="J167" s="10"/>
+    </row>
+    <row r="168" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A168" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D168" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E168" s="10">
+        <v>3</v>
+      </c>
+      <c r="F168" s="10"/>
+      <c r="G168" s="12"/>
+      <c r="H168" s="11"/>
+      <c r="I168" s="11"/>
+      <c r="J168" s="10"/>
+    </row>
+    <row r="169" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A169" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E169" s="10">
+        <v>3</v>
+      </c>
+      <c r="F169" s="10"/>
+      <c r="G169" s="12"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="11"/>
+      <c r="J169" s="10"/>
+    </row>
+    <row r="170" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A170" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D170" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E170" s="10">
+        <v>3</v>
+      </c>
+      <c r="F170" s="10"/>
+      <c r="G170" s="12"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="10"/>
+    </row>
+    <row r="171" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A171" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E171" s="10">
+        <v>3</v>
+      </c>
+      <c r="F171" s="10"/>
+      <c r="G171" s="12"/>
+      <c r="H171" s="11"/>
+      <c r="I171" s="11"/>
+      <c r="J171" s="10"/>
+    </row>
+    <row r="172" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A172" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E172" s="10">
+        <v>3</v>
+      </c>
+      <c r="F172" s="10"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="11"/>
+      <c r="I172" s="11"/>
+      <c r="J172" s="10"/>
+    </row>
+    <row r="173" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A173" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E173" s="10">
+        <v>3</v>
+      </c>
+      <c r="F173" s="10"/>
+      <c r="G173" s="12"/>
+      <c r="H173" s="11"/>
+      <c r="I173" s="11"/>
+      <c r="J173" s="10"/>
+    </row>
+    <row r="174" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A174" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E174" s="10">
+        <v>3</v>
+      </c>
+      <c r="F174" s="10"/>
+      <c r="G174" s="12"/>
+      <c r="H174" s="11"/>
+      <c r="I174" s="11"/>
+      <c r="J174" s="10"/>
+    </row>
+    <row r="175" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A175" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B175" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D175" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E175" s="10">
+        <v>3</v>
+      </c>
+      <c r="F175" s="10"/>
+      <c r="G175" s="12"/>
+      <c r="H175" s="11"/>
+      <c r="I175" s="11"/>
+      <c r="J175" s="10"/>
+    </row>
+    <row r="176" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A176" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E176" s="10">
+        <v>3</v>
+      </c>
+      <c r="F176" s="10"/>
+      <c r="G176" s="12"/>
+      <c r="H176" s="11"/>
+      <c r="I176" s="11"/>
+      <c r="J176" s="10"/>
+    </row>
+    <row r="177" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A177" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B177" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E177" s="10">
+        <v>3</v>
+      </c>
+      <c r="F177" s="10"/>
+      <c r="G177" s="12"/>
+      <c r="H177" s="11"/>
+      <c r="I177" s="11"/>
+      <c r="J177" s="10"/>
+    </row>
+    <row r="178" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="A178" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="E178" s="10">
+        <v>3</v>
+      </c>
+      <c r="F178" s="10"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="11"/>
+      <c r="I178" s="11"/>
+      <c r="J178" s="10"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A179" s="10"/>
+      <c r="B179" s="10"/>
+      <c r="C179" s="10"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="10"/>
+      <c r="F179" s="10"/>
+      <c r="G179" s="12"/>
+      <c r="H179" s="11"/>
+      <c r="I179" s="11"/>
+      <c r="J179" s="10"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A180" s="10"/>
+      <c r="B180" s="10"/>
+      <c r="C180" s="10"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="10"/>
+      <c r="F180" s="10"/>
+      <c r="G180" s="12"/>
+      <c r="H180" s="11"/>
+      <c r="I180" s="11"/>
+      <c r="J180" s="10"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A181" s="10"/>
+      <c r="B181" s="10"/>
+      <c r="C181" s="10"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="10"/>
+      <c r="F181" s="10"/>
+      <c r="G181" s="10"/>
+      <c r="H181" s="10"/>
+      <c r="I181" s="10"/>
+      <c r="J181" s="10"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="10"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="10"/>
+      <c r="F182" s="10"/>
+      <c r="G182" s="10"/>
+      <c r="H182" s="10"/>
+      <c r="I182" s="10"/>
+      <c r="J182" s="10"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="10"/>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10"/>
+      <c r="G183" s="10"/>
+      <c r="H183" s="10"/>
+      <c r="I183" s="10"/>
+      <c r="J183" s="10"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A184" s="10"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="10"/>
+      <c r="D184" s="10"/>
+      <c r="E184" s="10"/>
+      <c r="F184" s="10"/>
+      <c r="G184" s="10"/>
+      <c r="H184" s="10"/>
+      <c r="I184" s="10"/>
+      <c r="J184" s="10"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A185" s="10"/>
+      <c r="B185" s="10"/>
+      <c r="C185" s="10"/>
+      <c r="D185" s="10"/>
+      <c r="E185" s="10"/>
+      <c r="F185" s="10"/>
+      <c r="G185" s="10"/>
+      <c r="H185" s="10"/>
+      <c r="I185" s="10"/>
+      <c r="J185" s="10"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A186" s="10"/>
+      <c r="B186" s="10"/>
+      <c r="C186" s="10"/>
+      <c r="D186" s="10"/>
+      <c r="E186" s="10"/>
+      <c r="F186" s="10"/>
+      <c r="G186" s="10"/>
+      <c r="H186" s="10"/>
+      <c r="I186" s="10"/>
+      <c r="J186" s="10"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A187" s="10"/>
+      <c r="B187" s="10"/>
+      <c r="C187" s="10"/>
+      <c r="D187" s="10"/>
+      <c r="E187" s="10"/>
+      <c r="F187" s="10"/>
+      <c r="G187" s="10"/>
+      <c r="H187" s="10"/>
+      <c r="I187" s="10"/>
+      <c r="J187" s="10"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A188" s="10"/>
+      <c r="B188" s="10"/>
+      <c r="C188" s="10"/>
+      <c r="D188" s="10"/>
+      <c r="E188" s="10"/>
+      <c r="F188" s="10"/>
+      <c r="G188" s="10"/>
+      <c r="H188" s="10"/>
+      <c r="I188" s="10"/>
+      <c r="J188" s="10"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A189" s="10"/>
+      <c r="B189" s="10"/>
+      <c r="C189" s="10"/>
+      <c r="D189" s="10"/>
+      <c r="E189" s="10"/>
+      <c r="F189" s="10"/>
+      <c r="G189" s="10"/>
+      <c r="H189" s="10"/>
+      <c r="I189" s="10"/>
+      <c r="J189" s="10"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A190" s="10"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="10"/>
+      <c r="D190" s="10"/>
+      <c r="E190" s="10"/>
+      <c r="F190" s="10"/>
+      <c r="G190" s="10"/>
+      <c r="H190" s="10"/>
+      <c r="I190" s="10"/>
+      <c r="J190" s="10"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A191" s="10"/>
+      <c r="B191" s="10"/>
+      <c r="C191" s="10"/>
+      <c r="D191" s="10"/>
+      <c r="E191" s="10"/>
+      <c r="F191" s="10"/>
+      <c r="G191" s="10"/>
+      <c r="H191" s="10"/>
+      <c r="I191" s="10"/>
+      <c r="J191" s="10"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A192" s="10"/>
+      <c r="B192" s="10"/>
+      <c r="C192" s="10"/>
+      <c r="D192" s="10"/>
+      <c r="E192" s="10"/>
+      <c r="F192" s="10"/>
+      <c r="G192" s="10"/>
+      <c r="H192" s="10"/>
+      <c r="I192" s="10"/>
+      <c r="J192" s="10"/>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A193" s="10"/>
+      <c r="B193" s="10"/>
+      <c r="C193" s="10"/>
+      <c r="D193" s="10"/>
+      <c r="E193" s="10"/>
+      <c r="F193" s="10"/>
+      <c r="G193" s="10"/>
+      <c r="H193" s="10"/>
+      <c r="I193" s="10"/>
+      <c r="J193" s="10"/>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A194" s="10"/>
+      <c r="B194" s="10"/>
+      <c r="C194" s="10"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="10"/>
+      <c r="F194" s="10"/>
+      <c r="G194" s="10"/>
+      <c r="H194" s="10"/>
+      <c r="I194" s="10"/>
+      <c r="J194" s="10"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A195" s="10"/>
+      <c r="B195" s="10"/>
+      <c r="C195" s="10"/>
+      <c r="D195" s="10"/>
+      <c r="E195" s="10"/>
+      <c r="F195" s="10"/>
+      <c r="G195" s="10"/>
+      <c r="H195" s="10"/>
+      <c r="I195" s="10"/>
+      <c r="J195" s="10"/>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A196" s="10"/>
+      <c r="B196" s="10"/>
+      <c r="C196" s="10"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="10"/>
+      <c r="F196" s="10"/>
+      <c r="G196" s="10"/>
+      <c r="H196" s="10"/>
+      <c r="I196" s="10"/>
+      <c r="J196" s="10"/>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A197" s="10"/>
+      <c r="B197" s="10"/>
+      <c r="C197" s="10"/>
+      <c r="D197" s="10"/>
+      <c r="E197" s="10"/>
+      <c r="F197" s="10"/>
+      <c r="G197" s="10"/>
+      <c r="H197" s="10"/>
+      <c r="I197" s="10"/>
+      <c r="J197" s="10"/>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A198" s="10"/>
+      <c r="B198" s="10"/>
+      <c r="C198" s="10"/>
+      <c r="D198" s="10"/>
+      <c r="E198" s="10"/>
+      <c r="F198" s="10"/>
+      <c r="G198" s="10"/>
+      <c r="H198" s="10"/>
+      <c r="I198" s="10"/>
+      <c r="J198" s="10"/>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A199" s="10"/>
+      <c r="B199" s="10"/>
+      <c r="C199" s="10"/>
+      <c r="D199" s="10"/>
+      <c r="E199" s="10"/>
+      <c r="F199" s="10"/>
+      <c r="G199" s="10"/>
+      <c r="H199" s="10"/>
+      <c r="I199" s="10"/>
+      <c r="J199" s="10"/>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A200" s="10"/>
+      <c r="B200" s="10"/>
+      <c r="C200" s="10"/>
+      <c r="D200" s="10"/>
+      <c r="E200" s="10"/>
+      <c r="F200" s="10"/>
+      <c r="G200" s="10"/>
+      <c r="H200" s="10"/>
+      <c r="I200" s="10"/>
+      <c r="J200" s="10"/>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A201" s="10"/>
+      <c r="B201" s="10"/>
+      <c r="C201" s="10"/>
+      <c r="D201" s="10"/>
+      <c r="E201" s="10"/>
+      <c r="F201" s="10"/>
+      <c r="G201" s="10"/>
+      <c r="H201" s="10"/>
+      <c r="I201" s="10"/>
+      <c r="J201" s="10"/>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A202" s="10"/>
+      <c r="B202" s="10"/>
+      <c r="C202" s="10"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="10"/>
+      <c r="F202" s="10"/>
+      <c r="G202" s="10"/>
+      <c r="H202" s="10"/>
+      <c r="I202" s="10"/>
+      <c r="J202" s="10"/>
+    </row>
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A203" s="10"/>
+      <c r="B203" s="10"/>
+      <c r="C203" s="10"/>
+      <c r="D203" s="10"/>
+      <c r="E203" s="10"/>
+      <c r="F203" s="10"/>
+      <c r="G203" s="10"/>
+      <c r="H203" s="10"/>
+      <c r="I203" s="10"/>
+      <c r="J203" s="10"/>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A204" s="10"/>
+      <c r="B204" s="10"/>
+      <c r="C204" s="10"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="10"/>
+      <c r="F204" s="10"/>
+      <c r="G204" s="10"/>
+      <c r="H204" s="10"/>
+      <c r="I204" s="10"/>
+      <c r="J204" s="10"/>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A205" s="10"/>
+      <c r="B205" s="10"/>
+      <c r="C205" s="10"/>
+      <c r="D205" s="10"/>
+      <c r="E205" s="10"/>
+      <c r="F205" s="10"/>
+      <c r="G205" s="10"/>
+      <c r="H205" s="10"/>
+      <c r="I205" s="10"/>
+      <c r="J205" s="10"/>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A206" s="10"/>
+      <c r="B206" s="10"/>
+      <c r="C206" s="10"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="10"/>
+      <c r="F206" s="10"/>
+      <c r="G206" s="10"/>
+      <c r="H206" s="10"/>
+      <c r="I206" s="10"/>
+      <c r="J206" s="10"/>
+    </row>
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A207" s="10"/>
+      <c r="B207" s="10"/>
+      <c r="C207" s="10"/>
+      <c r="D207" s="10"/>
+      <c r="E207" s="10"/>
+      <c r="F207" s="10"/>
+      <c r="G207" s="10"/>
+      <c r="H207" s="10"/>
+      <c r="I207" s="10"/>
+      <c r="J207" s="10"/>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A208" s="10"/>
+      <c r="B208" s="10"/>
+      <c r="C208" s="10"/>
+      <c r="D208" s="10"/>
+      <c r="E208" s="10"/>
+      <c r="F208" s="10"/>
+      <c r="G208" s="10"/>
+      <c r="H208" s="10"/>
+      <c r="I208" s="10"/>
+      <c r="J208" s="10"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A209" s="10"/>
+      <c r="B209" s="10"/>
+      <c r="C209" s="10"/>
+      <c r="D209" s="10"/>
+      <c r="E209" s="10"/>
+      <c r="F209" s="10"/>
+      <c r="G209" s="10"/>
+      <c r="H209" s="10"/>
+      <c r="I209" s="10"/>
+      <c r="J209" s="10"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A210" s="10"/>
+      <c r="B210" s="10"/>
+      <c r="C210" s="10"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="10"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="10"/>
+      <c r="H210" s="10"/>
+      <c r="I210" s="10"/>
+      <c r="J210" s="10"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A211" s="10"/>
+      <c r="B211" s="10"/>
+      <c r="C211" s="10"/>
+      <c r="D211" s="10"/>
+      <c r="E211" s="10"/>
+      <c r="F211" s="10"/>
+      <c r="G211" s="10"/>
+      <c r="H211" s="10"/>
+      <c r="I211" s="10"/>
+      <c r="J211" s="10"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A212" s="10"/>
+      <c r="B212" s="10"/>
+      <c r="C212" s="10"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10"/>
+      <c r="F212" s="10"/>
+      <c r="G212" s="10"/>
+      <c r="H212" s="10"/>
+      <c r="I212" s="10"/>
+      <c r="J212" s="10"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A213" s="10"/>
+      <c r="B213" s="10"/>
+      <c r="C213" s="10"/>
+      <c r="D213" s="10"/>
+      <c r="E213" s="10"/>
+      <c r="F213" s="10"/>
+      <c r="G213" s="10"/>
+      <c r="H213" s="10"/>
+      <c r="I213" s="10"/>
+      <c r="J213" s="10"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A214" s="10"/>
+      <c r="B214" s="10"/>
+      <c r="C214" s="10"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="10"/>
+      <c r="F214" s="10"/>
+      <c r="G214" s="10"/>
+      <c r="H214" s="10"/>
+      <c r="I214" s="10"/>
+      <c r="J214" s="10"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A215" s="10"/>
+      <c r="B215" s="10"/>
+      <c r="C215" s="10"/>
+      <c r="D215" s="10"/>
+      <c r="E215" s="10"/>
+      <c r="F215" s="10"/>
+      <c r="G215" s="10"/>
+      <c r="H215" s="10"/>
+      <c r="I215" s="10"/>
+      <c r="J215" s="10"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A216" s="10"/>
+      <c r="B216" s="10"/>
+      <c r="C216" s="10"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="10"/>
+      <c r="F216" s="10"/>
+      <c r="G216" s="10"/>
+      <c r="H216" s="10"/>
+      <c r="I216" s="10"/>
+      <c r="J216" s="10"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A217" s="10"/>
+      <c r="B217" s="10"/>
+      <c r="C217" s="10"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="10"/>
+      <c r="F217" s="10"/>
+      <c r="G217" s="10"/>
+      <c r="H217" s="10"/>
+      <c r="I217" s="10"/>
+      <c r="J217" s="10"/>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A218" s="10"/>
+      <c r="B218" s="10"/>
+      <c r="C218" s="10"/>
+      <c r="D218" s="10"/>
+      <c r="E218" s="10"/>
+      <c r="F218" s="10"/>
+      <c r="G218" s="10"/>
+      <c r="H218" s="10"/>
+      <c r="I218" s="10"/>
+      <c r="J218" s="10"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A219" s="10"/>
+      <c r="B219" s="10"/>
+      <c r="C219" s="10"/>
+      <c r="D219" s="10"/>
+      <c r="E219" s="10"/>
+      <c r="F219" s="10"/>
+      <c r="G219" s="10"/>
+      <c r="H219" s="10"/>
+      <c r="I219" s="10"/>
+      <c r="J219" s="10"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A220" s="10"/>
+      <c r="B220" s="10"/>
+      <c r="C220" s="10"/>
+      <c r="D220" s="10"/>
+      <c r="E220" s="10"/>
+      <c r="F220" s="10"/>
+      <c r="G220" s="10"/>
+      <c r="H220" s="10"/>
+      <c r="I220" s="10"/>
+      <c r="J220" s="10"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10"/>
+      <c r="C221" s="10"/>
+      <c r="D221" s="10"/>
+      <c r="E221" s="10"/>
+      <c r="F221" s="10"/>
+      <c r="G221" s="10"/>
+      <c r="H221" s="10"/>
+      <c r="I221" s="10"/>
+      <c r="J221" s="10"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A222" s="10"/>
+      <c r="B222" s="10"/>
+      <c r="C222" s="10"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="10"/>
+      <c r="F222" s="10"/>
+      <c r="G222" s="10"/>
+      <c r="H222" s="10"/>
+      <c r="I222" s="10"/>
+      <c r="J222" s="10"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A223" s="10"/>
+      <c r="B223" s="10"/>
+      <c r="C223" s="10"/>
+      <c r="D223" s="10"/>
+      <c r="E223" s="10"/>
+      <c r="F223" s="10"/>
+      <c r="G223" s="10"/>
+      <c r="H223" s="10"/>
+      <c r="I223" s="10"/>
+      <c r="J223" s="10"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A224" s="10"/>
+      <c r="B224" s="10"/>
+      <c r="C224" s="10"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="10"/>
+      <c r="F224" s="10"/>
+      <c r="G224" s="10"/>
+      <c r="H224" s="10"/>
+      <c r="I224" s="10"/>
+      <c r="J224" s="10"/>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A225" s="10"/>
+      <c r="B225" s="10"/>
+      <c r="C225" s="10"/>
+      <c r="D225" s="10"/>
+      <c r="E225" s="10"/>
+      <c r="F225" s="10"/>
+      <c r="G225" s="10"/>
+      <c r="H225" s="10"/>
+      <c r="I225" s="10"/>
+      <c r="J225" s="10"/>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A226" s="10"/>
+      <c r="B226" s="10"/>
+      <c r="C226" s="10"/>
+      <c r="D226" s="10"/>
+      <c r="E226" s="10"/>
+      <c r="F226" s="10"/>
+      <c r="G226" s="10"/>
+      <c r="H226" s="10"/>
+      <c r="I226" s="10"/>
+      <c r="J226" s="10"/>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A227" s="10"/>
+      <c r="B227" s="10"/>
+      <c r="C227" s="10"/>
+      <c r="D227" s="10"/>
+      <c r="E227" s="10"/>
+      <c r="F227" s="10"/>
+      <c r="G227" s="10"/>
+      <c r="H227" s="10"/>
+      <c r="I227" s="10"/>
+      <c r="J227" s="10"/>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A228" s="10"/>
+      <c r="B228" s="10"/>
+      <c r="C228" s="10"/>
+      <c r="D228" s="10"/>
+      <c r="E228" s="10"/>
+      <c r="F228" s="10"/>
+      <c r="G228" s="10"/>
+      <c r="H228" s="10"/>
+      <c r="I228" s="10"/>
+      <c r="J228" s="10"/>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A229" s="10"/>
+      <c r="B229" s="10"/>
+      <c r="C229" s="10"/>
+      <c r="D229" s="10"/>
+      <c r="E229" s="10"/>
+      <c r="F229" s="10"/>
+      <c r="G229" s="10"/>
+      <c r="H229" s="10"/>
+      <c r="I229" s="10"/>
+      <c r="J229" s="10"/>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A230" s="10"/>
+      <c r="B230" s="10"/>
+      <c r="C230" s="10"/>
+      <c r="D230" s="10"/>
+      <c r="E230" s="10"/>
+      <c r="F230" s="10"/>
+      <c r="G230" s="10"/>
+      <c r="H230" s="10"/>
+      <c r="I230" s="10"/>
+      <c r="J230" s="10"/>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A231" s="10"/>
+      <c r="B231" s="10"/>
+      <c r="C231" s="10"/>
+      <c r="D231" s="10"/>
+      <c r="E231" s="10"/>
+      <c r="F231" s="10"/>
+      <c r="G231" s="10"/>
+      <c r="H231" s="10"/>
+      <c r="I231" s="10"/>
+      <c r="J231" s="10"/>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A232" s="10"/>
+      <c r="B232" s="10"/>
+      <c r="C232" s="10"/>
+      <c r="D232" s="10"/>
+      <c r="E232" s="10"/>
+      <c r="F232" s="10"/>
+      <c r="G232" s="10"/>
+      <c r="H232" s="10"/>
+      <c r="I232" s="10"/>
+      <c r="J232" s="10"/>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A233" s="10"/>
+      <c r="B233" s="10"/>
+      <c r="C233" s="10"/>
+      <c r="D233" s="10"/>
+      <c r="E233" s="10"/>
+      <c r="F233" s="10"/>
+      <c r="G233" s="10"/>
+      <c r="H233" s="10"/>
+      <c r="I233" s="10"/>
+      <c r="J233" s="10"/>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A234" s="10"/>
+      <c r="B234" s="10"/>
+      <c r="C234" s="10"/>
+      <c r="D234" s="10"/>
+      <c r="E234" s="10"/>
+      <c r="F234" s="10"/>
+      <c r="G234" s="10"/>
+      <c r="H234" s="10"/>
+      <c r="I234" s="10"/>
+      <c r="J234" s="10"/>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A235" s="10"/>
+      <c r="B235" s="10"/>
+      <c r="C235" s="10"/>
+      <c r="D235" s="10"/>
+      <c r="E235" s="10"/>
+      <c r="F235" s="10"/>
+      <c r="G235" s="10"/>
+      <c r="H235" s="10"/>
+      <c r="I235" s="10"/>
+      <c r="J235" s="10"/>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A236" s="10"/>
+      <c r="B236" s="10"/>
+      <c r="C236" s="10"/>
+      <c r="D236" s="10"/>
+      <c r="E236" s="10"/>
+      <c r="F236" s="10"/>
+      <c r="G236" s="10"/>
+      <c r="H236" s="10"/>
+      <c r="I236" s="10"/>
+      <c r="J236" s="10"/>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A237" s="10"/>
+      <c r="B237" s="10"/>
+      <c r="C237" s="10"/>
+      <c r="D237" s="10"/>
+      <c r="E237" s="10"/>
+      <c r="F237" s="10"/>
+      <c r="G237" s="10"/>
+      <c r="H237" s="10"/>
+      <c r="I237" s="10"/>
+      <c r="J237" s="10"/>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G238" s="10"/>
+      <c r="H238" s="10"/>
+      <c r="I238" s="10"/>
+      <c r="J238" s="10"/>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G239" s="10"/>
+      <c r="H239" s="10"/>
+      <c r="I239" s="10"/>
+      <c r="J239" s="10"/>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G240" s="10"/>
+      <c r="H240" s="10"/>
+      <c r="I240" s="10"/>
+      <c r="J240" s="10"/>
+    </row>
+    <row r="241" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G241" s="10"/>
+      <c r="H241" s="10"/>
+      <c r="I241" s="10"/>
+      <c r="J241" s="10"/>
+    </row>
+    <row r="242" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G242" s="10"/>
+      <c r="H242" s="10"/>
+      <c r="I242" s="10"/>
+      <c r="J242" s="10"/>
+    </row>
+    <row r="243" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G243" s="10"/>
+      <c r="H243" s="10"/>
+      <c r="I243" s="10"/>
+      <c r="J243" s="10"/>
+    </row>
+    <row r="244" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G244" s="10"/>
+      <c r="H244" s="10"/>
+      <c r="I244" s="10"/>
+      <c r="J244" s="10"/>
+    </row>
+    <row r="245" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G245" s="10"/>
+      <c r="H245" s="10"/>
+      <c r="I245" s="10"/>
+      <c r="J245" s="10"/>
+    </row>
+    <row r="246" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G246" s="10"/>
+      <c r="H246" s="10"/>
+      <c r="I246" s="10"/>
+      <c r="J246" s="10"/>
+    </row>
+    <row r="247" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G247" s="10"/>
+      <c r="H247" s="10"/>
+      <c r="I247" s="10"/>
+      <c r="J247" s="10"/>
+    </row>
+    <row r="248" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G248" s="10"/>
+      <c r="H248" s="10"/>
+      <c r="I248" s="10"/>
+      <c r="J248" s="10"/>
+    </row>
+    <row r="249" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G249" s="10"/>
+      <c r="H249" s="10"/>
+      <c r="I249" s="10"/>
+      <c r="J249" s="10"/>
+    </row>
+    <row r="250" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G250" s="10"/>
+      <c r="H250" s="10"/>
+      <c r="I250" s="10"/>
+      <c r="J250" s="10"/>
+    </row>
+    <row r="251" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G251" s="10"/>
+      <c r="H251" s="10"/>
+      <c r="I251" s="10"/>
+      <c r="J251" s="10"/>
+    </row>
+    <row r="252" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G252" s="10"/>
+      <c r="H252" s="10"/>
+      <c r="I252" s="10"/>
+      <c r="J252" s="10"/>
+    </row>
+    <row r="253" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G253" s="10"/>
+      <c r="H253" s="10"/>
+      <c r="I253" s="10"/>
+      <c r="J253" s="10"/>
+    </row>
+    <row r="254" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G254" s="10"/>
+      <c r="H254" s="10"/>
+      <c r="I254" s="10"/>
+      <c r="J254" s="10"/>
+    </row>
+    <row r="255" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G255" s="10"/>
+      <c r="H255" s="10"/>
+      <c r="I255" s="10"/>
+      <c r="J255" s="10"/>
+    </row>
+    <row r="256" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G256" s="10"/>
+      <c r="H256" s="10"/>
+      <c r="I256" s="10"/>
+      <c r="J256" s="10"/>
+    </row>
+    <row r="257" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G257" s="10"/>
+      <c r="H257" s="10"/>
+      <c r="I257" s="10"/>
+      <c r="J257" s="10"/>
+    </row>
+    <row r="258" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G258" s="10"/>
+      <c r="H258" s="10"/>
+      <c r="I258" s="10"/>
+      <c r="J258" s="10"/>
+    </row>
+    <row r="259" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G259" s="10"/>
+      <c r="H259" s="10"/>
+      <c r="I259" s="10"/>
+      <c r="J259" s="10"/>
+    </row>
+    <row r="260" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G260" s="10"/>
+      <c r="H260" s="10"/>
+      <c r="I260" s="10"/>
+      <c r="J260" s="10"/>
+    </row>
+    <row r="261" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G261" s="10"/>
+      <c r="H261" s="10"/>
+      <c r="I261" s="10"/>
+      <c r="J261" s="10"/>
+    </row>
+    <row r="262" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G262" s="10"/>
+      <c r="H262" s="10"/>
+      <c r="I262" s="10"/>
+      <c r="J262" s="10"/>
+    </row>
+    <row r="263" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G263" s="10"/>
+      <c r="H263" s="10"/>
+      <c r="I263" s="10"/>
+      <c r="J263" s="10"/>
+    </row>
+    <row r="264" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G264" s="10"/>
+      <c r="H264" s="10"/>
+      <c r="I264" s="10"/>
+      <c r="J264" s="10"/>
+    </row>
+    <row r="265" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G265" s="10"/>
+      <c r="H265" s="10"/>
+      <c r="I265" s="10"/>
+      <c r="J265" s="10"/>
+    </row>
+    <row r="266" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G266" s="10"/>
+      <c r="H266" s="10"/>
+      <c r="I266" s="10"/>
+      <c r="J266" s="10"/>
+    </row>
+    <row r="267" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G267" s="10"/>
+      <c r="H267" s="10"/>
+      <c r="I267" s="10"/>
+      <c r="J267" s="10"/>
+    </row>
+    <row r="268" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G268" s="10"/>
+      <c r="H268" s="10"/>
+      <c r="I268" s="10"/>
+      <c r="J268" s="10"/>
+    </row>
+    <row r="269" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G269" s="10"/>
+      <c r="H269" s="10"/>
+      <c r="I269" s="10"/>
+      <c r="J269" s="10"/>
+    </row>
+    <row r="270" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G270" s="10"/>
+      <c r="H270" s="10"/>
+      <c r="I270" s="10"/>
+      <c r="J270" s="10"/>
+    </row>
+    <row r="271" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G271" s="10"/>
+      <c r="H271" s="10"/>
+      <c r="I271" s="10"/>
+      <c r="J271" s="10"/>
+    </row>
+    <row r="272" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G272" s="10"/>
+      <c r="H272" s="10"/>
+      <c r="I272" s="10"/>
+      <c r="J272" s="10"/>
+    </row>
+    <row r="273" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G273" s="10"/>
+      <c r="H273" s="10"/>
+      <c r="I273" s="10"/>
+      <c r="J273" s="10"/>
+    </row>
+    <row r="274" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G274" s="10"/>
+      <c r="H274" s="10"/>
+      <c r="I274" s="10"/>
+      <c r="J274" s="10"/>
+    </row>
+    <row r="275" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G275" s="10"/>
+      <c r="H275" s="10"/>
+      <c r="I275" s="10"/>
+      <c r="J275" s="10"/>
+    </row>
+    <row r="276" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G276" s="10"/>
+      <c r="H276" s="10"/>
+      <c r="I276" s="10"/>
+      <c r="J276" s="10"/>
+    </row>
+    <row r="277" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G277" s="10"/>
+      <c r="H277" s="10"/>
+      <c r="I277" s="10"/>
+      <c r="J277" s="10"/>
+    </row>
+    <row r="278" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G278" s="10"/>
+      <c r="H278" s="10"/>
+      <c r="I278" s="10"/>
+      <c r="J278" s="10"/>
+    </row>
+    <row r="279" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G279" s="10"/>
+      <c r="H279" s="10"/>
+      <c r="I279" s="10"/>
+      <c r="J279" s="10"/>
+    </row>
+    <row r="280" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G280" s="10"/>
+      <c r="H280" s="10"/>
+      <c r="I280" s="10"/>
+      <c r="J280" s="10"/>
+    </row>
+    <row r="281" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G281" s="10"/>
+      <c r="H281" s="10"/>
+      <c r="I281" s="10"/>
+      <c r="J281" s="10"/>
+    </row>
+    <row r="282" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G282" s="10"/>
+      <c r="H282" s="10"/>
+      <c r="I282" s="10"/>
+      <c r="J282" s="10"/>
+    </row>
+    <row r="283" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G283" s="10"/>
+      <c r="H283" s="10"/>
+      <c r="I283" s="10"/>
+      <c r="J283" s="10"/>
+    </row>
+    <row r="284" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G284" s="10"/>
+      <c r="H284" s="10"/>
+      <c r="I284" s="10"/>
+      <c r="J284" s="10"/>
+    </row>
+    <row r="285" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G285" s="10"/>
+      <c r="H285" s="10"/>
+      <c r="I285" s="10"/>
+      <c r="J285" s="10"/>
+    </row>
+    <row r="286" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G286" s="10"/>
+      <c r="H286" s="10"/>
+      <c r="I286" s="10"/>
+      <c r="J286" s="10"/>
+    </row>
+    <row r="287" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G287" s="10"/>
+      <c r="H287" s="10"/>
+      <c r="I287" s="10"/>
+      <c r="J287" s="10"/>
+    </row>
+    <row r="288" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G288" s="10"/>
+      <c r="H288" s="10"/>
+      <c r="I288" s="10"/>
+      <c r="J288" s="10"/>
+    </row>
+    <row r="289" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G289" s="10"/>
+      <c r="H289" s="10"/>
+      <c r="I289" s="10"/>
+      <c r="J289" s="10"/>
+    </row>
+    <row r="290" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G290" s="10"/>
+      <c r="H290" s="10"/>
+      <c r="I290" s="10"/>
+      <c r="J290" s="10"/>
+    </row>
+    <row r="291" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G291" s="10"/>
+      <c r="H291" s="10"/>
+      <c r="I291" s="10"/>
+      <c r="J291" s="10"/>
+    </row>
+    <row r="292" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G292" s="10"/>
+      <c r="H292" s="10"/>
+      <c r="I292" s="10"/>
+      <c r="J292" s="10"/>
+    </row>
+    <row r="293" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G293" s="10"/>
+      <c r="H293" s="10"/>
+      <c r="I293" s="10"/>
+      <c r="J293" s="10"/>
+    </row>
+    <row r="294" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G294" s="10"/>
+      <c r="H294" s="10"/>
+      <c r="I294" s="10"/>
+      <c r="J294" s="10"/>
+    </row>
+    <row r="295" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G295" s="10"/>
+      <c r="H295" s="10"/>
+      <c r="I295" s="10"/>
+      <c r="J295" s="10"/>
+    </row>
+    <row r="296" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G296" s="10"/>
+      <c r="H296" s="10"/>
+      <c r="I296" s="10"/>
+      <c r="J296" s="10"/>
+    </row>
+    <row r="297" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G297" s="10"/>
+      <c r="H297" s="10"/>
+      <c r="I297" s="10"/>
+      <c r="J297" s="10"/>
+    </row>
+    <row r="298" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G298" s="10"/>
+      <c r="H298" s="10"/>
+      <c r="I298" s="10"/>
+      <c r="J298" s="10"/>
+    </row>
+    <row r="299" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G299" s="10"/>
+      <c r="H299" s="10"/>
+      <c r="I299" s="10"/>
+      <c r="J299" s="10"/>
+    </row>
+    <row r="300" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G300" s="10"/>
+      <c r="H300" s="10"/>
+      <c r="I300" s="10"/>
+      <c r="J300" s="10"/>
+    </row>
+    <row r="301" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G301" s="10"/>
+      <c r="H301" s="10"/>
+      <c r="I301" s="10"/>
+      <c r="J301" s="10"/>
+    </row>
+    <row r="302" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G302" s="10"/>
+      <c r="H302" s="10"/>
+      <c r="I302" s="10"/>
+      <c r="J302" s="10"/>
+    </row>
+    <row r="303" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G303" s="10"/>
+      <c r="H303" s="10"/>
+      <c r="I303" s="10"/>
+      <c r="J303" s="10"/>
+    </row>
+    <row r="304" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G304" s="10"/>
+      <c r="H304" s="10"/>
+      <c r="I304" s="10"/>
+      <c r="J304" s="10"/>
+    </row>
+    <row r="305" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G305" s="10"/>
+      <c r="H305" s="10"/>
+      <c r="I305" s="10"/>
+      <c r="J305" s="10"/>
+    </row>
+    <row r="306" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G306" s="10"/>
+      <c r="H306" s="10"/>
+      <c r="I306" s="10"/>
+      <c r="J306" s="10"/>
+    </row>
+    <row r="307" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G307" s="10"/>
+      <c r="H307" s="10"/>
+      <c r="I307" s="10"/>
+      <c r="J307" s="10"/>
+    </row>
+    <row r="308" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G308" s="10"/>
+      <c r="H308" s="10"/>
+      <c r="I308" s="10"/>
+      <c r="J308" s="10"/>
+    </row>
+    <row r="309" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G309" s="10"/>
+      <c r="H309" s="10"/>
+      <c r="I309" s="10"/>
+      <c r="J309" s="10"/>
+    </row>
+    <row r="310" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G310" s="10"/>
+      <c r="H310" s="10"/>
+      <c r="I310" s="10"/>
+      <c r="J310" s="10"/>
+    </row>
+    <row r="311" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G311" s="10"/>
+      <c r="H311" s="10"/>
+      <c r="I311" s="10"/>
+      <c r="J311" s="10"/>
+    </row>
+    <row r="312" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G312" s="10"/>
+      <c r="H312" s="10"/>
+      <c r="I312" s="10"/>
+      <c r="J312" s="10"/>
+    </row>
+    <row r="313" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G313" s="10"/>
+      <c r="H313" s="10"/>
+      <c r="I313" s="10"/>
+      <c r="J313" s="10"/>
+    </row>
+    <row r="314" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G314" s="10"/>
+      <c r="H314" s="10"/>
+      <c r="I314" s="10"/>
+      <c r="J314" s="10"/>
+    </row>
+    <row r="315" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G315" s="10"/>
+      <c r="H315" s="10"/>
+      <c r="I315" s="10"/>
+      <c r="J315" s="10"/>
+    </row>
+    <row r="316" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G316" s="10"/>
+      <c r="H316" s="10"/>
+      <c r="I316" s="10"/>
+      <c r="J316" s="10"/>
+    </row>
+    <row r="317" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G317" s="10"/>
+      <c r="H317" s="10"/>
+      <c r="I317" s="10"/>
+      <c r="J317" s="10"/>
+    </row>
+    <row r="318" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G318" s="10"/>
+      <c r="H318" s="10"/>
+      <c r="I318" s="10"/>
+      <c r="J318" s="10"/>
+    </row>
+    <row r="319" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G319" s="10"/>
+      <c r="H319" s="10"/>
+      <c r="I319" s="10"/>
+      <c r="J319" s="10"/>
+    </row>
+    <row r="320" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G320" s="10"/>
+      <c r="H320" s="10"/>
+      <c r="I320" s="10"/>
+      <c r="J320" s="10"/>
+    </row>
+    <row r="321" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G321" s="10"/>
+      <c r="H321" s="10"/>
+      <c r="I321" s="10"/>
+      <c r="J321" s="10"/>
+    </row>
+    <row r="322" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G322" s="10"/>
+      <c r="H322" s="10"/>
+      <c r="I322" s="10"/>
+      <c r="J322" s="10"/>
+    </row>
+    <row r="323" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G323" s="10"/>
+      <c r="H323" s="10"/>
+      <c r="I323" s="10"/>
+      <c r="J323" s="10"/>
+    </row>
+    <row r="324" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G324" s="10"/>
+      <c r="H324" s="10"/>
+      <c r="I324" s="10"/>
+      <c r="J324" s="10"/>
+    </row>
+    <row r="325" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G325" s="10"/>
+      <c r="H325" s="10"/>
+      <c r="I325" s="10"/>
+      <c r="J325" s="10"/>
+    </row>
+    <row r="326" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G326" s="10"/>
+      <c r="H326" s="10"/>
+      <c r="I326" s="10"/>
+      <c r="J326" s="10"/>
+    </row>
+    <row r="327" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G327" s="10"/>
+      <c r="H327" s="10"/>
+      <c r="I327" s="10"/>
+      <c r="J327" s="10"/>
+    </row>
+    <row r="328" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G328" s="10"/>
+      <c r="H328" s="10"/>
+      <c r="I328" s="10"/>
+      <c r="J328" s="10"/>
+    </row>
+    <row r="329" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G329" s="10"/>
+      <c r="H329" s="10"/>
+      <c r="I329" s="10"/>
+      <c r="J329" s="10"/>
+    </row>
+    <row r="330" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G330" s="10"/>
+      <c r="H330" s="10"/>
+      <c r="I330" s="10"/>
+      <c r="J330" s="10"/>
+    </row>
+    <row r="331" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G331" s="10"/>
+      <c r="H331" s="10"/>
+      <c r="I331" s="10"/>
+      <c r="J331" s="10"/>
+    </row>
+    <row r="332" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G332" s="10"/>
+      <c r="H332" s="10"/>
+      <c r="I332" s="10"/>
+      <c r="J332" s="10"/>
+    </row>
+    <row r="333" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G333" s="10"/>
+      <c r="H333" s="10"/>
+      <c r="I333" s="10"/>
+      <c r="J333" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
